--- a/data/vendor-search/results_all_robotvacuum.xlsx
+++ b/data/vendor-search/results_all_robotvacuum.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,8 +477,10 @@
       <c r="D2" t="n">
         <v>7.5</v>
       </c>
-      <c r="E2" t="n">
-        <v>3</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -483,6 +490,11 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>cpe:2.3:o:miele_professional:pst10_webserver:-:*:*:*:*:*:*:*|cpe:2.3:h:miele_professional:pg_8528:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>miele</t>
         </is>
       </c>
     </row>
@@ -505,8 +517,10 @@
       <c r="D3" t="n">
         <v>5.9</v>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -514,6 +528,11 @@
           <t>cpe:2.3:o:infineon:trusted_platform_firmware:4.31:*:*:*:*:*:*:*|cpe:2.3:o:infineon:trusted_platform_firmware:4.32:*:*:*:*:*:*:*|cpe:2.3:o:infineon:trusted_platform_firmware:6.40:*:*:*:*:*:*:*|cpe:2.3:o:infineon:trusted_platform_firmware:133.32:*:*:*:*:*:*:*|cpe:2.3:h:acer:c720_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebase:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebase_24:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_11_c730:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_11_c730e:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_11_c735:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_11_c740:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_11_c771:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_11_c771t:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_11_n7_c731:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_13_cb5-311:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_14_cb3-431:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_14_for_work_cp5-471:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_15_cb3-531:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_15_cb3-532:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_15_cb5-571:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_r11:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebook_r13_cb5-312t:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebox:-:*:*:*:*:*:*:*|cpe:2.3:h:acer:chromebox_cxi2:-:*:*:*:*:*:*:*|cpe:2.3:h:aopen:chromebase:-:*:commercial:*:*:*:*:*|cpe:2.3:h:aopen:chromebase:-:*:mini:*:*:*:*:*|cpe:2.3:h:aopen:chromebox:-:*:commercial:*:*:*:*:*|cpe:2.3:h:aopen:chromeboxi:-:*:mini:*:*:*:*:*|cpe:2.3:h:asi:chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:asus:chromebit_cs10:-:*:*:*:*:*:*:*|cpe:2.3:h:asus:chromebook_c200:-:*:*:*:*:*:*:*|cpe:2.3:h:asus:chromebook_c201pa:-:*:*:*:*:*:*:*|cpe:2.3:h:asus:chromebook_c202sa:-:*:*:*:*:*:*:*|cpe:2.3:h:asus:chromebook_c300:-:*:*:*:*:*:*:*|cpe:2.3:h:asus:chromebook_c300sa:-:*:*:*:*:*:*:*|cpe:2.3:h:asus:chromebook_c301sa:-:*:*:*:*:*:*:*|cpe:2.3:h:asus:chromebook_flip_c100pa:-:*:*:*:*:*:*:*|cpe:2.3:h:asus:chromebook_flip_c302:-:*:*:*:*:*:*:*|cpe:2.3:h:asus:chromebox_cn60:-:*:*:*:*:*:*:*|cpe:2.3:h:asus:chromebox_cn62:-:*:*:*:*:*:*:*|cpe:2.3:h:bobicus:chromebook_11:*:*:*:*:*:*:*:*|cpe:2.3:h:ctl:j2_chromebook:-:*:*:*:*:education:*:*|cpe:2.3:h:ctl:j4_chromebook:-:*:*:*:*:education:*:*|cpe:2.3:h:ctl:j5_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:ctl:n6_chromebook:-:*:*:*:*:education:*:*|cpe:2.3:h:ctl:nl61_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:dell:chromebook_11:-:*:*:*:*:*:*:*|cpe:2.3:h:dell:chromebook_11_3120:-:*:*:*:*:*:*:*|cpe:2.3:h:dell:chromebook_11_3189:-:*:*:*:*:*:*:*|cpe:2.3:h:dell:chromebook_11_model_3180:-:*:*:*:*:*:*:*|cpe:2.3:h:dell:chromebook_13_3380:-:*:*:*:*:*:*:*|cpe:2.3:h:dell:chromebox:-:*:*:*:*:*:*:*|cpe:2.3:h:edugear:chromebook_k:-:*:*:*:*:*:*:*|cpe:2.3:h:edugear:chromebook_m:-:*:*:*:*:*:*:*|cpe:2.3:h:edugear:chromebook_r:-:*:*:*:*:*:*:*|cpe:2.3:h:edugear:cmt_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:edxis:chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:edxis:education_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:epik:chromebook_elb1101:-:*:*:*:*:*:*:*|cpe:2.3:h:google:pixel:-:*:*:*:*:*:*:*|cpe:2.3:h:haier:chromebook_11:-:*:*:*:*:*:*:*|cpe:2.3:h:haier:chromebook_11_c:-:*:*:*:*:*:*:*|cpe:2.3:h:haier:chromebook_11_g2:-:*:*:*:*:*:*:*|cpe:2.3:h:haier:chromebook_11e:-:*:*:*:*:*:*:*|cpe:2.3:h:hexa:chromebook_pi:-:*:*:*:*:*:*:*|cpe:2.3:h:hisense:chromebook_11:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook:-:*:*:*:*:meetings:*:*|cpe:2.3:h:hp:chromebook_11-vxxx:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_11_1100-1199:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_11_2000-2099:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_11_2100-2199:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_11_2200-2299:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_11_g1:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_11_g2:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_11_g3:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_11_g4\/g4_ee:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_11_g5:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_11_g5_ee:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_13_g1:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_14:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_14_ak000-099:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_14_g3:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_14_g4:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebook_14_x000-x999:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebox_cb1-\(000-099\):-:*:*:*:*:*:*:*|cpe:2.3:h:hp:chromebox_g1:-:*:*:*:*:*:*:*|cpe:2.3:h:lenovo:100s_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:lenovo:n20_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:lenovo:n21_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:lenovo:n22_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:lenovo:n23_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:lenovo:n23_flex_11_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:lenovo:n23_yoga_11_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:lenovo:n42_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:lenovo:thinkcentre_chromebox:-:*:*:*:*:*:*:*|cpe:2.3:h:lenovo:thinkpad_11e_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:lenovo:thinkpad_13_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:lg:chromebase_22cb25s:-:*:*:*:*:*:*:*|cpe:2.3:h:lg:chromebase_22cv241:-:*:*:*:*:*:*:*|cpe:2.3:h:medion:akoya_s2013:-:*:*:*:*:*:*:*|cpe:2.3:h:medion:chromebook_s2015:-:*:*:*:*:*:*:*|cpe:2.3:h:mercer:chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:mercer:v2_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:ncomputing:chromebook_cx100:-:*:*:*:*:*:*:*|cpe:2.3:h:nexian:chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:pcmerge:chromebook_pcm-116t-432b:-:*:*:*:*:*:*:*|cpe:2.3:h:poin2:chromebook_11:-:*:*:*:*:*:*:*|cpe:2.3:h:poin2:chromebook_14:-:*:*:*:*:*:*:*|cpe:2.3:h:positivo:chromebook_ch1190:-:*:*:*:*:*:*:*|cpe:2.3:h:prowise:entry_line_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:prowise:proline_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:rgs:education_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:samsung:chromebook_2_11:-:*:*:*:*:*:*:*|cpe:2.3:h:samsung:chromebook_2_11_xe500c12:-:*:*:*:*:*:*:*|cpe:2.3:h:samsung:chromebook_2_13:-:*:*:*:*:*:*:*|cpe:2.3:h:samsung:chromebook_3:-:*:*:*:*:*:*:*|cpe:2.3:h:samsung:chromebook_plus:-:*:*:*:*:*:*:*|cpe:2.3:h:samsung:chromebook_pro:-:*:*:*:*:*:*:*|cpe:2.3:h:sector-five:e1_rugged_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:senkatel:c1101_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:toshiba:chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:toshiba:chromebook_2:-:*:*:*:*:*:*:*|cpe:2.3:h:toshiba:chromebook_2:-:*:2015:*:*:*:*:*|cpe:2.3:h:true:idc_chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:true:idc_chromebook_11:-:*:*:*:*:*:*:*|cpe:2.3:h:videonet:chromebook:-:*:*:*:*:*:*:*|cpe:2.3:h:videonet:chromebook_bl10:-:*:*:*:*:*:*:*|cpe:2.3:h:viglen:chromebook_11:-:*:*:*:*:*:*:*|cpe:2.3:h:viglen:chromebook_360:-:*:*:*:*:*:*:*|cpe:2.3:h:xolo:chromebook:-:*:*:*:*:*:*:*|cpe:2.3:a:infineon:rsa_library:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>medion</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -534,8 +553,10 @@
       <c r="D4" t="n">
         <v>7.5</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -545,6 +566,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>cpe:2.3:o:neatorobotics:botvac_d4_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d4_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d6_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d6_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d7_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d7_connected:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>neato</t>
         </is>
       </c>
     </row>
@@ -567,8 +593,10 @@
       <c r="D5" t="n">
         <v>2.4</v>
       </c>
-      <c r="E5" t="n">
-        <v>3.1</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -578,6 +606,11 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>cpe:2.3:o:neatorobotics:botvac_d4_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d4_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d6_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d6_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d5_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d5_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d7_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d7_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d3_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d3_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_85_firmware:1.2.1:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_85_connected:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>neato</t>
         </is>
       </c>
     </row>
@@ -600,8 +633,10 @@
       <c r="D6" t="n">
         <v>5.3</v>
       </c>
-      <c r="E6" t="n">
-        <v>3.1</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -609,6 +644,11 @@
           <t>cpe:2.3:o:neatorobotics:botvac_d4_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d4_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d6_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d6_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d5_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d5_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d7_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d7_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d3_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d3_connected:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>neato</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -629,8 +669,10 @@
       <c r="D7" t="n">
         <v>8.1</v>
       </c>
-      <c r="E7" t="n">
-        <v>3</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -640,6 +682,11 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>cpe:2.3:o:neatorobotics:botvac_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_connected:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>neato</t>
         </is>
       </c>
     </row>
@@ -662,8 +709,10 @@
       <c r="D8" t="n">
         <v>7.4</v>
       </c>
-      <c r="E8" t="n">
-        <v>3</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -671,6 +720,11 @@
           <t>cpe:2.3:o:neatorobotics:botvac_d4_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d4_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d6_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d6_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d5_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d5_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d7_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d7_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d3_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d3_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_d3_pro_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_d3_pro_connected:-:*:*:*:*:*:*:*|cpe:2.3:o:neatorobotics:botvac_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_connected:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>neato</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -691,8 +745,10 @@
       <c r="D9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E9" t="n">
-        <v>3</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -702,6 +758,11 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>cpe:2.3:o:axentra:hipserv:-:*:*:*:*:*:*:*|cpe:2.3:h:medion:lifecloud:-:*:*:*:*:*:*:*|cpe:2.3:h:netgear:stora:-:*:*:*:*:*:*:*|cpe:2.3:h:seagate:goflex_home:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>medion</t>
         </is>
       </c>
     </row>
@@ -724,8 +785,10 @@
       <c r="D10" t="n">
         <v>5.6</v>
       </c>
-      <c r="E10" t="n">
-        <v>3</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -735,6 +798,11 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>cpe:2.3:o:jisiwei:i3_firmware:2.0:*:*:*:*:*:*:*|cpe:2.3:h:jisiwei:i3:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>robot vacuum</t>
         </is>
       </c>
     </row>
@@ -757,8 +825,10 @@
       <c r="D11" t="n">
         <v>4.8</v>
       </c>
-      <c r="E11" t="n">
-        <v>3</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -768,6 +838,11 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>cpe:2.3:o:jisiwei:i3_firmware:2.0:*:*:*:*:*:*:*|cpe:2.3:h:jisiwei:i3:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>robot vacuum</t>
         </is>
       </c>
     </row>
@@ -790,8 +865,10 @@
       <c r="D12" t="n">
         <v>4.7</v>
       </c>
-      <c r="E12" t="n">
-        <v>3.1</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -801,6 +878,11 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>cpe:2.3:o:neatorobotics:botvac_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_connected:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>neato</t>
         </is>
       </c>
     </row>
@@ -823,8 +905,10 @@
       <c r="D13" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="n">
-        <v>3.1</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -834,6 +918,11 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -856,8 +945,10 @@
       <c r="D14" t="n">
         <v>9</v>
       </c>
-      <c r="E14" t="n">
-        <v>3.1</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -867,6 +958,11 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -889,8 +985,10 @@
       <c r="D15" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E15" t="n">
-        <v>3.1</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -900,6 +998,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.8.5h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -922,8 +1025,10 @@
       <c r="D16" t="n">
         <v>7.3</v>
       </c>
-      <c r="E16" t="n">
-        <v>3.1</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -933,6 +1038,11 @@
       <c r="G16" t="inlineStr">
         <is>
           <t>cpe:2.3:a:miele:benchmark_programming_tool:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>miele</t>
         </is>
       </c>
     </row>
@@ -955,8 +1065,10 @@
       <c r="D17" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E17" t="n">
-        <v>3.1</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -966,6 +1078,11 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.8.5h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -988,8 +1105,10 @@
       <c r="D18" t="n">
         <v>6.5</v>
       </c>
-      <c r="E18" t="n">
-        <v>3.1</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -999,6 +1118,11 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.8.5h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -1021,8 +1145,10 @@
       <c r="D19" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E19" t="n">
-        <v>3.1</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1032,6 +1158,11 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>cpe:2.3:a:uclibc:uclibc:0.9.33.2:*:*:*:*:*:*:*|cpe:2.3:a:uclibc-ng_project:uclibc-ng:1.0.40:*:*:*:*:*:*:*|cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.8.8h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -1054,8 +1185,10 @@
       <c r="D20" t="n">
         <v>8.1</v>
       </c>
-      <c r="E20" t="n">
-        <v>3.1</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1065,6 +1198,11 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>cpe:2.3:a:miele:appwash:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>miele</t>
         </is>
       </c>
     </row>
@@ -1087,8 +1225,10 @@
       <c r="D21" t="n">
         <v>7.5</v>
       </c>
-      <c r="E21" t="n">
-        <v>3.1</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1098,6 +1238,11 @@
       <c r="G21" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tapo:mini_smart_wi-fi_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:tapo:mini_smart_wi-fi_plug:-:*:*:*:*:*:*:*|cpe:2.3:o:nanoleaf:lightstrip_firmware:3.5.10:*:*:*:*:*:*:*|cpe:2.3:h:nanoleaf:lightstrip:-:*:*:*:*:*:*:*|cpe:2.3:o:govee:led_strip_firmware:3.00.42:*:*:*:*:*:*:*|cpe:2.3:h:govee:led_strip:-:*:*:*:*:*:*:*|cpe:2.3:o:switchbot:hub2_firmware:1.0-0.8:*:*:*:*:*:*:*|cpe:2.3:h:switchbot:hub2:-:*:*:*:*:*:*:*|cpe:2.3:o:phillips:hue_bridge_firmware:1.59.1959097030:*:*:*:*:*:*:*|cpe:2.3:h:phillips:hue_bridge:-:*:*:*:*:*:*:*|cpe:2.3:o:yeelight:smart_lamp_firmware:1.12.69:*:*:*:*:*:*:*|cpe:2.3:h:yeelight:smart_lamp:-:*:*:*:*:*:*:*|cpe:2.3:o:tp-link:smart_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:smart_plug:-:*:*:*:*:*:*:*|cpe:2.3:o:orein:smart_bulb_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:orein:smart_bulb:-:*:*:*:*:*:*:*|cpe:2.3:o:eve:eve_door_and_window_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:eve:eve_door_and_window:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>switchbot</t>
         </is>
       </c>
     </row>
@@ -1120,8 +1265,10 @@
       <c r="D22" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="E22" t="n">
-        <v>3.1</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1131,6 +1278,11 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>cpe:2.3:o:eufy:homebase_2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:eufy:homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -1153,8 +1305,10 @@
       <c r="D23" t="n">
         <v>9.1</v>
       </c>
-      <c r="E23" t="n">
-        <v>3.1</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1162,6 +1316,11 @@
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>switchbot</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1182,8 +1341,10 @@
       <c r="D24" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E24" t="n">
-        <v>2</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1193,6 +1354,11 @@
       <c r="G24" t="inlineStr">
         <is>
           <t>cpe:2.3:a:staruml:staruml:5.0.2.1570:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>neato</t>
         </is>
       </c>
     </row>
@@ -1215,8 +1381,10 @@
       <c r="D25" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E25" t="n">
-        <v>3</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1226,6 +1394,11 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>cpe:2.3:o:neatorobotics:botvac_connected_firmware:2.2.0:*:*:*:*:*:*:*|cpe:2.3:h:neatorobotics:botvac_connected:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>neato</t>
         </is>
       </c>
     </row>
@@ -1248,8 +1421,10 @@
       <c r="D26" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E26" t="n">
-        <v>3.1</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1259,6 +1434,11 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>cpe:2.3:o:miele:xgw_3000_zigbee_gateway_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:miele:xgw_3000_zigbee_gateway:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>miele</t>
         </is>
       </c>
     </row>
@@ -1281,8 +1461,10 @@
       <c r="D27" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E27" t="n">
-        <v>3.1</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1292,6 +1474,11 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>cpe:2.3:o:miele:xgw_3000_zigbee_gateway_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:miele:xgw_3000_zigbee_gateway:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>miele</t>
         </is>
       </c>
     </row>
@@ -1314,8 +1501,10 @@
       <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E28" t="n">
-        <v>3.1</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1325,6 +1514,11 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -1347,8 +1541,10 @@
       <c r="D29" t="n">
         <v>10</v>
       </c>
-      <c r="E29" t="n">
-        <v>3.1</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1358,6 +1554,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -1380,8 +1581,10 @@
       <c r="D30" t="n">
         <v>9.9</v>
       </c>
-      <c r="E30" t="n">
-        <v>3.1</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1391,6 +1594,11 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -1413,8 +1621,10 @@
       <c r="D31" t="n">
         <v>7.5</v>
       </c>
-      <c r="E31" t="n">
-        <v>3.1</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1424,6 +1634,11 @@
       <c r="G31" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -1446,8 +1661,10 @@
       <c r="D32" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E32" t="n">
-        <v>3.1</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1457,6 +1674,11 @@
       <c r="G32" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -1479,8 +1701,10 @@
       <c r="D33" t="n">
         <v>8.1</v>
       </c>
-      <c r="E33" t="n">
-        <v>3.1</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1490,6 +1714,11 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -1512,8 +1741,10 @@
       <c r="D34" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E34" t="n">
-        <v>3.1</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1523,6 +1754,11 @@
       <c r="G34" t="inlineStr">
         <is>
           <t>cpe:2.3:o:eufylife:solo_indoorcam_c24_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:eufylife:solo_indoorcam_c24:-:*:*:*:*:*:*:*|cpe:2.3:o:eufylife:solo_indoorcam_p24_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:eufylife:solo_indoorcam_p24:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>eufy</t>
         </is>
       </c>
     </row>
@@ -1545,8 +1781,10 @@
       <c r="D35" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E35" t="n">
-        <v>3.1</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1556,6 +1794,11 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>cpe:2.3:a:imoulife:life:*:*:*:*:*:android:*:*</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>imou</t>
         </is>
       </c>
     </row>
@@ -1578,8 +1821,10 @@
       <c r="D36" t="n">
         <v>8.1</v>
       </c>
-      <c r="E36" t="n">
-        <v>3.1</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1589,6 +1834,11 @@
       <c r="G36" t="inlineStr">
         <is>
           <t>cpe:2.3:a:imoulife:imou_life:6.7.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>imou</t>
         </is>
       </c>
     </row>
@@ -1611,8 +1861,10 @@
       <c r="D37" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E37" t="n">
-        <v>3.1</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1622,6 +1874,11 @@
       <c r="G37" t="inlineStr">
         <is>
           <t>cpe:2.3:a:imoulife:imou_go:1.0.11:*:*:*:*:android:*:*</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>imou</t>
         </is>
       </c>
     </row>
@@ -1644,8 +1901,10 @@
       <c r="D38" t="n">
         <v>7.4</v>
       </c>
-      <c r="E38" t="n">
-        <v>3.1</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1653,6 +1912,11 @@
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ecovacs</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1673,8 +1937,10 @@
       <c r="D39" t="n">
         <v>9.6</v>
       </c>
-      <c r="E39" t="n">
-        <v>3.1</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1684,6 +1950,11 @@
       <c r="G39" t="inlineStr">
         <is>
           <t>cpe:2.3:o:ecovacs:goat_g1-2000_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:goat_g1-2000:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:goat_g1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:goat_g1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:goat_g1-800_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:goat_g1-800:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:gx-600_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:gx-600:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x2_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x2_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x2_combo_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x2_combo:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x2s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x2s:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x5_pro_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x5_pro:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x5_pro_plus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x5_pro_plus:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x5_pro_ultra_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x5_pro_ultra:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t30_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t30_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t30s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t30s:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ecovacs</t>
         </is>
       </c>
     </row>
@@ -1706,8 +1977,10 @@
       <c r="D40" t="n">
         <v>7.6</v>
       </c>
-      <c r="E40" t="n">
-        <v>3.1</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1717,6 +1990,11 @@
       <c r="G40" t="inlineStr">
         <is>
           <t>cpe:2.3:o:ecovacs:deebot_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_900:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_n8_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n8:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t8_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t8:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_n9_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n9:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t9_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t9:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_n10_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x2_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x2:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:goat_g1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:goat_g1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_z1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_z1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_ava_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_ava:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_andy_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_andy:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ecovacs</t>
         </is>
       </c>
     </row>
@@ -1739,8 +2017,10 @@
       <c r="D41" t="n">
         <v>6.3</v>
       </c>
-      <c r="E41" t="n">
-        <v>3.1</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1750,6 +2030,11 @@
       <c r="G41" t="inlineStr">
         <is>
           <t>cpe:2.3:o:ecovacs:deebot_n10_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x2_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x2:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:goat_g1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:goat_g1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_z1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_z1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_ava_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_ava:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_andy_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_andy:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_900:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_n8_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n8:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t8_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t8:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_n9_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n9:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t9_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t9:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ecovacs</t>
         </is>
       </c>
     </row>
@@ -1772,8 +2057,10 @@
       <c r="D42" t="n">
         <v>3.3</v>
       </c>
-      <c r="E42" t="n">
-        <v>3.1</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1783,6 +2070,11 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>cpe:2.3:o:ecovacs:deebot_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_900:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_n8_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n8:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t8_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t8:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_n9_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n9:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t9_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t9:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_n10_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x2_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x2:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:goat_g1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:goat_g1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_z1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_z1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_ava_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_ava:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_andy_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_andy:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ecovacs</t>
         </is>
       </c>
     </row>
@@ -1805,8 +2097,10 @@
       <c r="D43" t="n">
         <v>6.5</v>
       </c>
-      <c r="E43" t="n">
-        <v>3.1</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1816,6 +2110,11 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>cpe:2.3:a:ecovacs:home:*:*:*:*:*:android:*:*|cpe:2.3:a:ecovacs:home:*:*:*:*:*:iphone_os:*:*</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ecovacs</t>
         </is>
       </c>
     </row>
@@ -1838,8 +2137,10 @@
       <c r="D44" t="n">
         <v>2.3</v>
       </c>
-      <c r="E44" t="n">
-        <v>3.1</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1849,6 +2150,11 @@
       <c r="G44" t="inlineStr">
         <is>
           <t>cpe:2.3:o:ecovacs:deebot_n8_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n8:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_900:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t8_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t8:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_n9_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n9:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t9_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t9:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_n10_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x2_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x2:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:goat_g1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:goat_g1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_z1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_z1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_ava_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_ava:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_andy_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_andy:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ecovacs</t>
         </is>
       </c>
     </row>
@@ -1871,8 +2177,10 @@
       <c r="D45" t="n">
         <v>7.4</v>
       </c>
-      <c r="E45" t="n">
-        <v>3.1</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1882,6 +2190,11 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>cpe:2.3:a:ecovacs:home:*:*:*:*:*:android:*:*|cpe:2.3:a:ecovacs:home:*:*:*:*:*:iphone_os:*:*</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ecovacs</t>
         </is>
       </c>
     </row>
@@ -1904,8 +2217,10 @@
       <c r="D46" t="n">
         <v>7.4</v>
       </c>
-      <c r="E46" t="n">
-        <v>3.1</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1915,6 +2230,11 @@
       <c r="G46" t="inlineStr">
         <is>
           <t>cpe:2.3:o:ecovacs:deebot_x2_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x2_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x2_combo_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x2_combo:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x2s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x2s:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x5_pro_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x5_pro:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x5_pro_plus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x5_pro_plus:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x5_pro_ultra_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x5_pro_ultra:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:mate_x_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:mate_x:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_turbo_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1_turbo:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_pro_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1_pro_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_plus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1_plus:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1s_pro_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1s_pro:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1s_pro_plus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1s_pro_plus:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1e_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1e_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_turbo_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10_turbo:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_plus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10_plus:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x2_pro_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x2_pro:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ecovacs</t>
         </is>
       </c>
     </row>
@@ -1937,8 +2257,10 @@
       <c r="D47" t="n">
         <v>7.5</v>
       </c>
-      <c r="E47" t="n">
-        <v>3.1</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1948,6 +2270,11 @@
       <c r="G47" t="inlineStr">
         <is>
           <t>cpe:2.3:o:ecovacs:deebot_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_900:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_n8_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n8:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t8_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t8:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_n9_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n9:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t9_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t9:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_n10_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_n10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x2_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x2:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:goat_g1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:goat_g1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_z1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_z1:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_ava_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_ava:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:airbot_andy_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:airbot_andy:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ecovacs</t>
         </is>
       </c>
     </row>
@@ -1975,6 +2302,11 @@
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ecovacs</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1995,8 +2327,10 @@
       <c r="D49" t="n">
         <v>5.1</v>
       </c>
-      <c r="E49" t="n">
-        <v>3</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2004,6 +2338,11 @@
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>switchbot</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2024,8 +2363,10 @@
       <c r="D50" t="n">
         <v>7.5</v>
       </c>
-      <c r="E50" t="n">
-        <v>3.1</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2033,6 +2374,11 @@
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ecovacs</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2053,8 +2399,10 @@
       <c r="D51" t="n">
         <v>6.3</v>
       </c>
-      <c r="E51" t="n">
-        <v>3.1</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2064,6 +2412,11 @@
       <c r="G51" t="inlineStr">
         <is>
           <t>cpe:2.3:o:ecovacs:deebot_x1s_pro_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1s_pro:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_pro_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1_pro_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_turbo_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1_turbo:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_plus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10_plus:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_turbo_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10_turbo:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_pro_plus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20_pro_plus:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_pro_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20_pro:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t30_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t30_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t30s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t30s:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ecovacs|robot vacuum</t>
         </is>
       </c>
     </row>
@@ -2086,8 +2439,10 @@
       <c r="D52" t="n">
         <v>7.2</v>
       </c>
-      <c r="E52" t="n">
-        <v>3.1</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2097,6 +2452,11 @@
       <c r="G52" t="inlineStr">
         <is>
           <t>cpe:2.3:o:ecovacs:deebot_x1s_pro_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1s_pro:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_pro_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1_pro_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_turbo_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1_turbo:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_plus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10_plus:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_turbo_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10_turbo:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_pro_plus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20_pro_plus:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_pro_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20_pro:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t30_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t30_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t30s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t30s:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ecovacs</t>
         </is>
       </c>
     </row>
@@ -2119,8 +2479,10 @@
       <c r="D53" t="n">
         <v>6.3</v>
       </c>
-      <c r="E53" t="n">
-        <v>3.1</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2130,6 +2492,11 @@
       <c r="G53" t="inlineStr">
         <is>
           <t>cpe:2.3:o:ecovacs:deebot_x1s_pro_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1s_pro:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_pro_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1_pro_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_x1_turbo_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_x1_turbo:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_plus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10_plus:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t10_turbo_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t10_turbo:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_pro_plus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20_pro_plus:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t20_pro_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t20_pro:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t30_omni_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t30_omni:-:*:*:*:*:*:*:*|cpe:2.3:o:ecovacs:deebot_t30s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecovacs:deebot_t30s:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ecovacs|robot vacuum</t>
         </is>
       </c>
     </row>
@@ -2152,8 +2519,10 @@
       <c r="D54" t="n">
         <v>7.7</v>
       </c>
-      <c r="E54" t="n">
-        <v>3.1</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2161,6 +2530,11 @@
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>eufy</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2181,8 +2555,10 @@
       <c r="D55" t="n">
         <v>7.1</v>
       </c>
-      <c r="E55" t="n">
-        <v>3.1</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2190,6 +2566,11 @@
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>irobot</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
